--- a/results/Int Task Remove ACC 0.2/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5167472939177119</v>
+        <v>0.5443723466231505</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5182124246432929</v>
+        <v>0.5456977878199742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5234269639414334</v>
+        <v>0.5468413751371951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5135653338225685</v>
+        <v>0.5492231781620849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5196382878054904</v>
+        <v>0.5390560978985416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5083115269610446</v>
+        <v>0.5377335534891805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.539652514250585</v>
+        <v>0.5384828558461999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5261753715129921</v>
+        <v>0.5368751388043992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5105652276070283</v>
+        <v>0.5413490661079086</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5105652276070283</v>
+        <v>0.5413490661079086</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5133863767304282</v>
+        <v>0.526479534196576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5197808741217101</v>
+        <v>0.5303016843209769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5248920946670143</v>
+        <v>0.5303016843209769</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5257505093517955</v>
+        <v>0.5303016843209769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5377873049898774</v>
+        <v>0.5335390052431853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5369288903050962</v>
+        <v>0.5443288948112099</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5364196994422075</v>
+        <v>0.5519091438705587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5371603114368387</v>
+        <v>0.5568050365478019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5511321611000068</v>
+        <v>0.556738088570886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.529795390245551</v>
+        <v>0.5528039293312605</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5175374731644828</v>
+        <v>0.5370338183843006</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5525071695489702</v>
+        <v>0.5293051894338068</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5300718725156024</v>
+        <v>0.5268390577072249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.523358728503423</v>
+        <v>0.5363121964408138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5273962064958849</v>
+        <v>0.5321685029080527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5169642311121411</v>
+        <v>0.5305607858662521</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5274354740592683</v>
+        <v>0.5287348441689278</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5300078213261493</v>
+        <v>0.521327758626794</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5300078213261493</v>
+        <v>0.521327758626794</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5313303657355104</v>
+        <v>0.5083453228147762</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5374396904943528</v>
+        <v>0.4906736318311881</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5508659785187117</v>
+        <v>0.4898879586982481</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5598138331257303</v>
+        <v>0.4900669157903885</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5598138331257303</v>
+        <v>0.4939283334781727</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5605660322702124</v>
+        <v>0.4944317307661359</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5605660322702124</v>
+        <v>0.5002951504559222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5783964028337019</v>
+        <v>0.4979934918841671</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5757542108024423</v>
+        <v>0.4994615193972107</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5596377728210525</v>
+        <v>0.507681958485817</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5564107515876004</v>
+        <v>0.522945775357351</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5714112826653019</v>
+        <v>0.5186202279449867</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5824528708773081</v>
+        <v>0.5227668182652105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5705834451815159</v>
+        <v>0.5235219141971553</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5738162599898935</v>
+        <v>0.5277354524942949</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5689406448248893</v>
+        <v>0.5367444615033039</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5715828368561487</v>
+        <v>0.5247018722902967</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5770461780108083</v>
+        <v>0.4978509055679474</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5950584024539008</v>
+        <v>0.4979934918841671</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6354737374029978</v>
+        <v>0.4949962824560895</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6435850641638423</v>
+        <v>0.4955695245084312</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6559215163716772</v>
+        <v>0.4969561201072455</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5831217069159191</v>
+        <v>0.4946995226737992</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5426204339387619</v>
+        <v>0.4965618351470442</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5296264109768933</v>
+        <v>0.4936650476843403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5457312618084322</v>
+        <v>0.491839105987016</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5424678697990595</v>
+        <v>0.4950545400706172</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5416458258901988</v>
+        <v>0.4959071611804731</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5388159864044109</v>
+        <v>0.4973693951185912</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5402083755781505</v>
+        <v>0.4973693951185912</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.569564741590465</v>
+        <v>0.5159445619252694</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5529085355451915</v>
+        <v>0.5119376611338026</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5534425100341499</v>
+        <v>0.5013122447206049</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5772483094026503</v>
+        <v>0.4794588801019669</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5565938929282981</v>
+        <v>0.4861443437006138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5676325843528416</v>
+        <v>0.4883980443465974</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5676325843528416</v>
+        <v>0.4859843766596178</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5640199685215762</v>
+        <v>0.4861633337517582</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5273453517826507</v>
+        <v>0.4793076034233591</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5383331884939602</v>
+        <v>0.4806665186086408</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5229734557708834</v>
+        <v>0.4801660181081403</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5228308694546637</v>
+        <v>0.4849920660210049</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5219026100055039</v>
+        <v>0.4792348618715178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5151328177051649</v>
+        <v>0.4741265381136764</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.510600632787128</v>
+        <v>0.4774903520884228</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5107068483274271</v>
+        <v>0.4737045727399425</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4987138263665595</v>
+        <v>0.482754458638703</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.49921432686706</v>
+        <v>0.4752585382810463</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.4678382562626935</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4987138263665595</v>
+        <v>0.4664094963130333</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4990717405508402</v>
+        <v>0.4667310397213934</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4985712400503397</v>
+        <v>0.4686297229705589</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.4759743666496078</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4785467139164888</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4785467139164888</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5002211214429864</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.499826836482785</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5050079017924677</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5008584146847812</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5003579141842808</v>
       </c>
     </row>
   </sheetData>
